--- a/DataAnalysis/AdditionalModels/Discriminators/LF/0.3/CLSDIV/res_scrimin=0.csv.xlsx
+++ b/DataAnalysis/AdditionalModels/Discriminators/LF/0.3/CLSDIV/res_scrimin=0.csv.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\Discriminators\CI\0.3\CLSDIV\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\AdditionalModels\Discriminators\LF\0.3\CLSDIV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B26C381B-A411-48BB-AAA8-319D4561F0EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48025001-2E07-4F4C-B249-304817E5B0E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0F214021-6FB1-40D5-9709-F0BEE25B15FC}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="37">
   <si>
     <t>Procedo per riga (prima riga, poi seconda riga, …)</t>
   </si>
@@ -129,6 +129,21 @@
   </si>
   <si>
     <t>Acc</t>
+  </si>
+  <si>
+    <t>Matrix</t>
+  </si>
+  <si>
+    <t>Class 0</t>
+  </si>
+  <si>
+    <t>Class 1</t>
+  </si>
+  <si>
+    <t>Class 2</t>
+  </si>
+  <si>
+    <t>CM</t>
   </si>
 </sst>
 </file>
@@ -997,7 +1012,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDEE7005-D29F-4A3A-8B33-A4338B8F6744}">
-  <dimension ref="A1:AL44"/>
+  <dimension ref="A1:AL40"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="8.88671875" customWidth="1"/>
@@ -1005,10 +1020,18 @@
   <sheetData>
     <row r="1" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1107,36 +1130,64 @@
       </c>
     </row>
     <row r="2" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
+      <c r="A2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="1">
+        <v>141</v>
+      </c>
+      <c r="D2" s="1">
+        <v>56</v>
+      </c>
+      <c r="E2" s="1">
+        <v>3</v>
+      </c>
       <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
+      <c r="G2" s="1">
+        <v>141</v>
+      </c>
+      <c r="H2" s="1">
+        <v>56</v>
+      </c>
+      <c r="I2" s="1">
+        <v>3</v>
+      </c>
+      <c r="J2" s="1">
+        <v>6</v>
+      </c>
+      <c r="K2" s="1">
+        <v>191</v>
+      </c>
+      <c r="L2" s="1">
+        <v>3</v>
+      </c>
+      <c r="M2" s="1">
+        <v>8</v>
+      </c>
+      <c r="N2" s="1">
+        <v>16</v>
+      </c>
+      <c r="O2" s="1">
+        <v>176</v>
+      </c>
       <c r="P2" s="1">
         <f>G2+K2+O2</f>
-        <v>0</v>
+        <v>508</v>
       </c>
       <c r="Q2" s="1">
         <f>G2+J2+M2</f>
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="R2" s="1">
         <f>H2+K2+N2</f>
-        <v>0</v>
+        <v>263</v>
       </c>
       <c r="S2" s="1">
         <f>I2+L2+O2</f>
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="T2" s="1">
         <v>200</v>
@@ -1147,29 +1198,29 @@
       <c r="V2" s="1">
         <v>200</v>
       </c>
-      <c r="W2" s="1" t="e">
+      <c r="W2" s="1">
         <f>G2/Q2</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X2" s="1" t="e">
+        <v>0.9096774193548387</v>
+      </c>
+      <c r="X2" s="1">
         <f>K2/R2</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y2" s="1" t="e">
+        <v>0.72623574144486691</v>
+      </c>
+      <c r="Y2" s="1">
         <f>O2/S2</f>
-        <v>#DIV/0!</v>
+        <v>0.96703296703296704</v>
       </c>
       <c r="Z2" s="1">
         <f>G2/T2</f>
-        <v>0</v>
+        <v>0.70499999999999996</v>
       </c>
       <c r="AA2" s="1">
         <f>K2/U2</f>
-        <v>0</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="AB2" s="1">
         <f>O2/V2</f>
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="AC2" s="1">
         <f>SUM(T2:V2)</f>
@@ -1177,171 +1228,459 @@
       </c>
       <c r="AD2" s="1">
         <f>P2/AC2</f>
-        <v>0</v>
-      </c>
-      <c r="AF2" t="e">
-        <f t="shared" ref="AF2:AK2" si="0">AVERAGE(W2:W10)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG2" t="e">
+        <v>0.84666666666666668</v>
+      </c>
+      <c r="AF2">
+        <f>AVERAGE(W2:W8)</f>
+        <v>0.89520313706921806</v>
+      </c>
+      <c r="AG2">
+        <f>AVERAGE(X2:X8)</f>
+        <v>0.69801060571950302</v>
+      </c>
+      <c r="AH2">
+        <f>AVERAGE(Y2:Y8)</f>
+        <v>0.95694356238233524</v>
+      </c>
+      <c r="AI2">
+        <f>AVERAGE(Z2:Z8)</f>
+        <v>0.627</v>
+      </c>
+      <c r="AJ2">
+        <f>AVERAGE(AA2:AA8)</f>
+        <v>0.94199999999999995</v>
+      </c>
+      <c r="AK2">
+        <f>AVERAGE(AB2:AB8)</f>
+        <v>0.90599999999999992</v>
+      </c>
+      <c r="AL2">
+        <f>AVERAGE(AD2:AD8)</f>
+        <v>0.82499999999999996</v>
+      </c>
+    </row>
+    <row r="3" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="1">
+        <v>6</v>
+      </c>
+      <c r="D3" s="1">
+        <v>191</v>
+      </c>
+      <c r="E3" s="1">
+        <v>3</v>
+      </c>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1">
+        <v>126</v>
+      </c>
+      <c r="H3" s="1">
+        <v>71</v>
+      </c>
+      <c r="I3" s="1">
+        <v>3</v>
+      </c>
+      <c r="J3" s="1">
+        <v>6</v>
+      </c>
+      <c r="K3" s="1">
+        <v>191</v>
+      </c>
+      <c r="L3" s="1">
+        <v>3</v>
+      </c>
+      <c r="M3" s="1">
+        <v>5</v>
+      </c>
+      <c r="N3" s="1">
+        <v>6</v>
+      </c>
+      <c r="O3" s="1">
+        <v>189</v>
+      </c>
+      <c r="P3" s="1">
+        <f t="shared" ref="P3:P6" si="0">G3+K3+O3</f>
+        <v>506</v>
+      </c>
+      <c r="Q3" s="1">
+        <f t="shared" ref="Q3:Q6" si="1">G3+J3+M3</f>
+        <v>137</v>
+      </c>
+      <c r="R3" s="1">
+        <f t="shared" ref="R3:R6" si="2">H3+K3+N3</f>
+        <v>268</v>
+      </c>
+      <c r="S3" s="1">
+        <f t="shared" ref="S3:S6" si="3">I3+L3+O3</f>
+        <v>195</v>
+      </c>
+      <c r="T3" s="1">
+        <v>200</v>
+      </c>
+      <c r="U3" s="1">
+        <v>200</v>
+      </c>
+      <c r="V3" s="1">
+        <v>200</v>
+      </c>
+      <c r="W3" s="1">
+        <f t="shared" ref="W3:W6" si="4">G3/Q3</f>
+        <v>0.91970802919708028</v>
+      </c>
+      <c r="X3" s="1">
+        <f t="shared" ref="X3:X6" si="5">K3/R3</f>
+        <v>0.71268656716417911</v>
+      </c>
+      <c r="Y3" s="1">
+        <f t="shared" ref="Y3:Y6" si="6">O3/S3</f>
+        <v>0.96923076923076923</v>
+      </c>
+      <c r="Z3" s="1">
+        <f t="shared" ref="Z3:Z6" si="7">G3/T3</f>
+        <v>0.63</v>
+      </c>
+      <c r="AA3" s="1">
+        <f t="shared" ref="AA3:AA6" si="8">K3/U3</f>
+        <v>0.95499999999999996</v>
+      </c>
+      <c r="AB3" s="1">
+        <f t="shared" ref="AB3:AB6" si="9">O3/V3</f>
+        <v>0.94499999999999995</v>
+      </c>
+      <c r="AC3" s="1">
+        <f t="shared" ref="AC3:AC6" si="10">SUM(T3:V3)</f>
+        <v>600</v>
+      </c>
+      <c r="AD3" s="1">
+        <f t="shared" ref="AD3:AD6" si="11">P3/AC3</f>
+        <v>0.84333333333333338</v>
+      </c>
+    </row>
+    <row r="4" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="1">
+        <v>8</v>
+      </c>
+      <c r="D4" s="1">
+        <v>16</v>
+      </c>
+      <c r="E4" s="1">
+        <v>176</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1">
+        <v>138</v>
+      </c>
+      <c r="H4" s="1">
+        <v>59</v>
+      </c>
+      <c r="I4" s="1">
+        <v>3</v>
+      </c>
+      <c r="J4" s="1">
+        <v>13</v>
+      </c>
+      <c r="K4" s="1">
+        <v>186</v>
+      </c>
+      <c r="L4" s="1">
+        <v>1</v>
+      </c>
+      <c r="M4" s="1">
+        <v>10</v>
+      </c>
+      <c r="N4" s="1">
+        <v>11</v>
+      </c>
+      <c r="O4" s="1">
+        <v>179</v>
+      </c>
+      <c r="P4" s="1">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH2" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AI2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AJ2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AK2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AL2">
-        <f>AVERAGE(AD2:AD10)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
-      <c r="P3" s="1"/>
-      <c r="Q3" s="1"/>
-      <c r="R3" s="1"/>
-      <c r="S3" s="1"/>
-      <c r="T3" s="1"/>
-      <c r="U3" s="1"/>
-      <c r="V3" s="1"/>
-      <c r="W3" s="1"/>
-      <c r="X3" s="1"/>
-      <c r="Y3" s="1"/>
-      <c r="Z3" s="1"/>
-      <c r="AA3" s="1"/>
-      <c r="AB3" s="1"/>
-      <c r="AC3" s="1"/>
-      <c r="AD3" s="1"/>
-    </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1"/>
-      <c r="Q4" s="1"/>
-      <c r="R4" s="1"/>
-      <c r="S4" s="1"/>
-      <c r="T4" s="1"/>
-      <c r="U4" s="1"/>
-      <c r="V4" s="1"/>
-      <c r="W4" s="1"/>
-      <c r="X4" s="1"/>
-      <c r="Y4" s="1"/>
-      <c r="Z4" s="1"/>
-      <c r="AA4" s="1"/>
-      <c r="AB4" s="1"/>
-      <c r="AC4" s="1"/>
-      <c r="AD4" s="1"/>
+        <v>503</v>
+      </c>
+      <c r="Q4" s="1">
+        <f t="shared" si="1"/>
+        <v>161</v>
+      </c>
+      <c r="R4" s="1">
+        <f t="shared" si="2"/>
+        <v>256</v>
+      </c>
+      <c r="S4" s="1">
+        <f t="shared" si="3"/>
+        <v>183</v>
+      </c>
+      <c r="T4" s="1">
+        <v>200</v>
+      </c>
+      <c r="U4" s="1">
+        <v>200</v>
+      </c>
+      <c r="V4" s="1">
+        <v>200</v>
+      </c>
+      <c r="W4" s="1">
+        <f t="shared" si="4"/>
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="X4" s="1">
+        <f t="shared" si="5"/>
+        <v>0.7265625</v>
+      </c>
+      <c r="Y4" s="1">
+        <f t="shared" si="6"/>
+        <v>0.97814207650273222</v>
+      </c>
+      <c r="Z4" s="1">
+        <f t="shared" si="7"/>
+        <v>0.69</v>
+      </c>
+      <c r="AA4" s="1">
+        <f t="shared" si="8"/>
+        <v>0.93</v>
+      </c>
+      <c r="AB4" s="1">
+        <f t="shared" si="9"/>
+        <v>0.89500000000000002</v>
+      </c>
+      <c r="AC4" s="1">
+        <f t="shared" si="10"/>
+        <v>600</v>
+      </c>
+      <c r="AD4" s="1">
+        <f t="shared" si="11"/>
+        <v>0.83833333333333337</v>
+      </c>
     </row>
     <row r="5" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
+      <c r="B5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
-      <c r="P5" s="1"/>
-      <c r="Q5" s="1"/>
-      <c r="R5" s="1"/>
-      <c r="S5" s="1"/>
-      <c r="T5" s="1"/>
-      <c r="U5" s="1"/>
-      <c r="V5" s="1"/>
-      <c r="W5" s="1"/>
-      <c r="X5" s="1"/>
-      <c r="Y5" s="1"/>
-      <c r="Z5" s="1"/>
-      <c r="AA5" s="1"/>
-      <c r="AB5" s="1"/>
-      <c r="AC5" s="1"/>
-      <c r="AD5" s="1"/>
+      <c r="G5" s="1">
+        <v>116</v>
+      </c>
+      <c r="H5" s="1">
+        <v>78</v>
+      </c>
+      <c r="I5" s="1">
+        <v>6</v>
+      </c>
+      <c r="J5" s="1">
+        <v>7</v>
+      </c>
+      <c r="K5" s="1">
+        <v>190</v>
+      </c>
+      <c r="L5" s="1">
+        <v>3</v>
+      </c>
+      <c r="M5" s="1">
+        <v>3</v>
+      </c>
+      <c r="N5" s="1">
+        <v>10</v>
+      </c>
+      <c r="O5" s="1">
+        <v>187</v>
+      </c>
+      <c r="P5" s="1">
+        <f t="shared" si="0"/>
+        <v>493</v>
+      </c>
+      <c r="Q5" s="1">
+        <f t="shared" si="1"/>
+        <v>126</v>
+      </c>
+      <c r="R5" s="1">
+        <f t="shared" si="2"/>
+        <v>278</v>
+      </c>
+      <c r="S5" s="1">
+        <f t="shared" si="3"/>
+        <v>196</v>
+      </c>
+      <c r="T5" s="1">
+        <v>200</v>
+      </c>
+      <c r="U5" s="1">
+        <v>200</v>
+      </c>
+      <c r="V5" s="1">
+        <v>200</v>
+      </c>
+      <c r="W5" s="1">
+        <f t="shared" si="4"/>
+        <v>0.92063492063492058</v>
+      </c>
+      <c r="X5" s="1">
+        <f t="shared" si="5"/>
+        <v>0.68345323741007191</v>
+      </c>
+      <c r="Y5" s="1">
+        <f t="shared" si="6"/>
+        <v>0.95408163265306123</v>
+      </c>
+      <c r="Z5" s="1">
+        <f t="shared" si="7"/>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="AA5" s="1">
+        <f t="shared" si="8"/>
+        <v>0.95</v>
+      </c>
+      <c r="AB5" s="1">
+        <f t="shared" si="9"/>
+        <v>0.93500000000000005</v>
+      </c>
+      <c r="AC5" s="1">
+        <f t="shared" si="10"/>
+        <v>600</v>
+      </c>
+      <c r="AD5" s="1">
+        <f t="shared" si="11"/>
+        <v>0.82166666666666666</v>
+      </c>
     </row>
     <row r="6" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
+      <c r="A6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="1">
+        <v>126</v>
+      </c>
+      <c r="D6" s="1">
+        <v>71</v>
+      </c>
+      <c r="E6" s="1">
+        <v>3</v>
+      </c>
       <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1"/>
-      <c r="Q6" s="1"/>
-      <c r="R6" s="1"/>
-      <c r="S6" s="1"/>
-      <c r="T6" s="1"/>
-      <c r="U6" s="1"/>
-      <c r="V6" s="1"/>
-      <c r="W6" s="1"/>
-      <c r="X6" s="1"/>
-      <c r="Y6" s="1"/>
-      <c r="Z6" s="1"/>
-      <c r="AA6" s="1"/>
-      <c r="AB6" s="1"/>
-      <c r="AC6" s="1"/>
-      <c r="AD6" s="1"/>
+      <c r="G6" s="1">
+        <v>106</v>
+      </c>
+      <c r="H6" s="1">
+        <v>86</v>
+      </c>
+      <c r="I6" s="1">
+        <v>8</v>
+      </c>
+      <c r="J6" s="1">
+        <v>8</v>
+      </c>
+      <c r="K6" s="1">
+        <v>184</v>
+      </c>
+      <c r="L6" s="1">
+        <v>8</v>
+      </c>
+      <c r="M6" s="1">
+        <v>8</v>
+      </c>
+      <c r="N6" s="1">
+        <v>17</v>
+      </c>
+      <c r="O6" s="1">
+        <v>175</v>
+      </c>
+      <c r="P6" s="1">
+        <f t="shared" si="0"/>
+        <v>465</v>
+      </c>
+      <c r="Q6" s="1">
+        <f t="shared" si="1"/>
+        <v>122</v>
+      </c>
+      <c r="R6" s="1">
+        <f t="shared" si="2"/>
+        <v>287</v>
+      </c>
+      <c r="S6" s="1">
+        <f t="shared" si="3"/>
+        <v>191</v>
+      </c>
+      <c r="T6" s="1">
+        <v>200</v>
+      </c>
+      <c r="U6" s="1">
+        <v>200</v>
+      </c>
+      <c r="V6" s="1">
+        <v>200</v>
+      </c>
+      <c r="W6" s="1">
+        <f t="shared" si="4"/>
+        <v>0.86885245901639341</v>
+      </c>
+      <c r="X6" s="1">
+        <f t="shared" si="5"/>
+        <v>0.64111498257839716</v>
+      </c>
+      <c r="Y6" s="1">
+        <f t="shared" si="6"/>
+        <v>0.91623036649214662</v>
+      </c>
+      <c r="Z6" s="1">
+        <f t="shared" si="7"/>
+        <v>0.53</v>
+      </c>
+      <c r="AA6" s="1">
+        <f t="shared" si="8"/>
+        <v>0.92</v>
+      </c>
+      <c r="AB6" s="1">
+        <f t="shared" si="9"/>
+        <v>0.875</v>
+      </c>
+      <c r="AC6" s="1">
+        <f t="shared" si="10"/>
+        <v>600</v>
+      </c>
+      <c r="AD6" s="1">
+        <f t="shared" si="11"/>
+        <v>0.77500000000000002</v>
+      </c>
     </row>
     <row r="7" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
+      <c r="A7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="1">
+        <v>6</v>
+      </c>
+      <c r="D7" s="1">
+        <v>191</v>
+      </c>
+      <c r="E7" s="1">
+        <v>3</v>
+      </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
@@ -1369,11 +1708,21 @@
       <c r="AD7" s="1"/>
     </row>
     <row r="8" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
+      <c r="A8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="1">
+        <v>5</v>
+      </c>
+      <c r="D8" s="1">
+        <v>6</v>
+      </c>
+      <c r="E8" s="1">
+        <v>189</v>
+      </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
@@ -1402,10 +1751,18 @@
     </row>
     <row r="9" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
+      <c r="B9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
@@ -1433,11 +1790,21 @@
       <c r="AD9" s="1"/>
     </row>
     <row r="10" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
+      <c r="A10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="1">
+        <v>138</v>
+      </c>
+      <c r="D10" s="1">
+        <v>59</v>
+      </c>
+      <c r="E10" s="1">
+        <v>3</v>
+      </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
@@ -1465,11 +1832,21 @@
       <c r="AD10" s="1"/>
     </row>
     <row r="11" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
+      <c r="A11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="1">
+        <v>13</v>
+      </c>
+      <c r="D11" s="1">
+        <v>186</v>
+      </c>
+      <c r="E11" s="1">
+        <v>1</v>
+      </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
@@ -1497,11 +1874,21 @@
       <c r="AD11" s="1"/>
     </row>
     <row r="12" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
+      <c r="A12" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="1">
+        <v>10</v>
+      </c>
+      <c r="D12" s="1">
+        <v>11</v>
+      </c>
+      <c r="E12" s="1">
+        <v>179</v>
+      </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
@@ -1530,10 +1917,18 @@
     </row>
     <row r="13" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
+      <c r="B13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
@@ -1561,11 +1956,21 @@
       <c r="AD13" s="1"/>
     </row>
     <row r="14" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
+      <c r="A14" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="1">
+        <v>116</v>
+      </c>
+      <c r="D14" s="1">
+        <v>78</v>
+      </c>
+      <c r="E14" s="1">
+        <v>6</v>
+      </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
@@ -1593,11 +1998,21 @@
       <c r="AD14" s="1"/>
     </row>
     <row r="15" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
+      <c r="A15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="1">
+        <v>7</v>
+      </c>
+      <c r="D15" s="1">
+        <v>190</v>
+      </c>
+      <c r="E15" s="1">
+        <v>3</v>
+      </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
@@ -1625,11 +2040,21 @@
       <c r="AD15" s="1"/>
     </row>
     <row r="16" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
+      <c r="A16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="1">
+        <v>3</v>
+      </c>
+      <c r="D16" s="1">
+        <v>10</v>
+      </c>
+      <c r="E16" s="1">
+        <v>187</v>
+      </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
@@ -1658,10 +2083,18 @@
     </row>
     <row r="17" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
+      <c r="B17" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
@@ -1689,11 +2122,21 @@
       <c r="AD17" s="1"/>
     </row>
     <row r="18" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
+      <c r="A18" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="1">
+        <v>106</v>
+      </c>
+      <c r="D18" s="1">
+        <v>86</v>
+      </c>
+      <c r="E18" s="1">
+        <v>8</v>
+      </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
@@ -1721,11 +2164,21 @@
       <c r="AD18" s="1"/>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
+      <c r="A19" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="1">
+        <v>8</v>
+      </c>
+      <c r="D19" s="1">
+        <v>184</v>
+      </c>
+      <c r="E19" s="1">
+        <v>8</v>
+      </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
@@ -1753,11 +2206,21 @@
       <c r="AD19" s="1"/>
     </row>
     <row r="20" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
+      <c r="A20" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="1">
+        <v>8</v>
+      </c>
+      <c r="D20" s="1">
+        <v>17</v>
+      </c>
+      <c r="E20" s="1">
+        <v>175</v>
+      </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
@@ -2424,134 +2887,6 @@
       <c r="AC40" s="1"/>
       <c r="AD40" s="1"/>
     </row>
-    <row r="41" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A41" s="1"/>
-      <c r="B41" s="1"/>
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
-      <c r="M41" s="1"/>
-      <c r="N41" s="1"/>
-      <c r="O41" s="1"/>
-      <c r="P41" s="1"/>
-      <c r="Q41" s="1"/>
-      <c r="R41" s="1"/>
-      <c r="S41" s="1"/>
-      <c r="T41" s="1"/>
-      <c r="U41" s="1"/>
-      <c r="V41" s="1"/>
-      <c r="W41" s="1"/>
-      <c r="X41" s="1"/>
-      <c r="Y41" s="1"/>
-      <c r="Z41" s="1"/>
-      <c r="AA41" s="1"/>
-      <c r="AB41" s="1"/>
-      <c r="AC41" s="1"/>
-      <c r="AD41" s="1"/>
-    </row>
-    <row r="42" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A42" s="1"/>
-      <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
-      <c r="K42" s="1"/>
-      <c r="L42" s="1"/>
-      <c r="M42" s="1"/>
-      <c r="N42" s="1"/>
-      <c r="O42" s="1"/>
-      <c r="P42" s="1"/>
-      <c r="Q42" s="1"/>
-      <c r="R42" s="1"/>
-      <c r="S42" s="1"/>
-      <c r="T42" s="1"/>
-      <c r="U42" s="1"/>
-      <c r="V42" s="1"/>
-      <c r="W42" s="1"/>
-      <c r="X42" s="1"/>
-      <c r="Y42" s="1"/>
-      <c r="Z42" s="1"/>
-      <c r="AA42" s="1"/>
-      <c r="AB42" s="1"/>
-      <c r="AC42" s="1"/>
-      <c r="AD42" s="1"/>
-    </row>
-    <row r="43" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A43" s="1"/>
-      <c r="B43" s="1"/>
-      <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1"/>
-      <c r="K43" s="1"/>
-      <c r="L43" s="1"/>
-      <c r="M43" s="1"/>
-      <c r="N43" s="1"/>
-      <c r="O43" s="1"/>
-      <c r="P43" s="1"/>
-      <c r="Q43" s="1"/>
-      <c r="R43" s="1"/>
-      <c r="S43" s="1"/>
-      <c r="T43" s="1"/>
-      <c r="U43" s="1"/>
-      <c r="V43" s="1"/>
-      <c r="W43" s="1"/>
-      <c r="X43" s="1"/>
-      <c r="Y43" s="1"/>
-      <c r="Z43" s="1"/>
-      <c r="AA43" s="1"/>
-      <c r="AB43" s="1"/>
-      <c r="AC43" s="1"/>
-      <c r="AD43" s="1"/>
-    </row>
-    <row r="44" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
-      <c r="C44" s="1"/>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
-      <c r="M44" s="1"/>
-      <c r="N44" s="1"/>
-      <c r="O44" s="1"/>
-      <c r="P44" s="1"/>
-      <c r="Q44" s="1"/>
-      <c r="R44" s="1"/>
-      <c r="S44" s="1"/>
-      <c r="T44" s="1"/>
-      <c r="U44" s="1"/>
-      <c r="V44" s="1"/>
-      <c r="W44" s="1"/>
-      <c r="X44" s="1"/>
-      <c r="Y44" s="1"/>
-      <c r="Z44" s="1"/>
-      <c r="AA44" s="1"/>
-      <c r="AB44" s="1"/>
-      <c r="AC44" s="1"/>
-      <c r="AD44" s="1"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
